--- a/results/link-prediction-gcn/Link/5shot/Cora/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/Cora/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.4946±0.0076</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.5433±0.0613</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4905±0.0112</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5209±0.0384</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.4943±0.0000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4915±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5424±0.0599</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5870±0.0616</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5870±0.0616</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5870±0.0616</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5427±0.0604</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5743±0.0190</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.6259±0.0117</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5063±0.0089</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.5582±0.0565</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.5089±0.0211</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5297±0.0220</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6436±0.0616</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6445±0.0755</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6645±0.0398</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5484±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4934±0.0081</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4937±0.0089</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4915±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4915±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6347±0.0039</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6392±0.0113</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6392±0.0113</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6392±0.0113</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5867±0.0614</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6664±0.0076</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5958±0.0266</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5430±0.0044</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4832±0.0080</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5351±0.0388</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.6613±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.6793±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6917±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5044±0.0063</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6546±0.0586</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.7081±0.0075</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.7081±0.0075</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7081±0.0075</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6164±0.0495</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6954±0.0154</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6654±0.0368</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5098±0.0107</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4994±0.0012</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0197</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.5019±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4915±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5383±0.0541</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5854±0.0605</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5854±0.0605</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5854±0.0605</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5430±0.0608</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6686±0.0371</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5775±0.0549</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.4994±0.0009</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.5025±0.0036</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.5114±0.0223</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.6433±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.6433±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.6433±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.5414±0.0586</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5376±0.0532</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5376±0.0532</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5376±0.0532</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.5376±0.0532</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5765±0.0543</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5689±0.0492</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5247±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.6433±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5750±0.0573</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4975±0.0004</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5231±0.0271</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0.5057±0.0056</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5389±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4915±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4848±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.7116±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.7049±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.7049±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.7049±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.6831±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6736±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7087±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4953±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.6271±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5958±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4934±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4801±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4810±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4877±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6546±0.0000</t>
+          <t>0.5525±0.0417</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5038±0.0000</t>
+          <t>0.5266±0.0043</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5038±0.0000</t>
+          <t>0.5266±0.0043</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5038±0.0000</t>
+          <t>0.5266±0.0043</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5104±0.0000</t>
+          <t>0.5117±0.0035</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6082±0.0000</t>
+          <t>0.5930±0.0107</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5038±0.0000</t>
+          <t>0.5288±0.0065</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.6585±0.0116</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.6733±0.0093</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.6498±0.0075</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6521±0.0184</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6616±0.0000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6551±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6747±0.0114</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6943±0.0202</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6943±0.0202</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6943±0.0202</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6765±0.0139</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6346±0.0097</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7125±0.0051</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6062±0.0855</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6863±0.0176</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6550±0.0023</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6518±0.0056</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7243±0.0262</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7273±0.0322</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7425±0.0200</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.4444±0.3143</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6377±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6563±0.0111</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6576±0.0128</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6873±0.0075</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7001±0.0095</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7001±0.0095</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7001±0.0095</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6761±0.0085</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7382±0.0060</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6784±0.0042</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.2222±0.3143</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6861±0.0022</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6440±0.0118</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6597±0.0229</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6564±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6533±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6687±0.0028</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7378±0.0269</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7647±0.0047</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7647±0.0047</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7647±0.0047</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7200±0.0224</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7589±0.0069</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7430±0.0171</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.5798±0.0656</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6648±0.0016</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6671±0.0010</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.7422±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.6658±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.6658±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6658±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.7459±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7609±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6685±0.0025</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6817±0.0124</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6817±0.0124</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6817±0.0124</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6712±0.0064</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7442±0.0185</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6760±0.0094</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.6586±0.0115</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6640±0.0037</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6601±0.0045</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6546±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6703±0.0051</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6672±0.0008</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6672±0.0008</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6672±0.0008</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6668±0.0003</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6890±0.0158</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6826±0.0126</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6948±0.0207</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6598±0.0044</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6581±0.0102</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0.6672±0.0005</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7044±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7044±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7044±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6958±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6840±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6564±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6476±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7662±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7670±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7670±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7670±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7537±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7386±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7683±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6611±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7246±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6682±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6594±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6376±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6385±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6405±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7161±0.0000</t>
+          <t>0.6873±0.0157</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.6781±0.0018</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.6781±0.0018</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.6781±0.0018</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6713±0.0000</t>
+          <t>0.6716±0.0019</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7110±0.0000</t>
+          <t>0.7053±0.0035</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.6789±0.0032</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6003±0.0000</t>
+          <t>0.5366±0.0474</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6904±0.0000</t>
+          <t>0.6773±0.0237</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5608±0.0000</t>
+          <t>0.6414±0.0158</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6469±0.0000</t>
+          <t>0.6733±0.0300</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6823±0.0000</t>
+          <t>0.6910±0.0127</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6800±0.0000</t>
+          <t>0.6887±0.0164</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6855±0.0000</t>
+          <t>0.6772±0.0178</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7150±0.0000</t>
+          <t>0.6911±0.0312</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7150±0.0000</t>
+          <t>0.6911±0.0312</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7150±0.0000</t>
+          <t>0.6911±0.0312</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.6845±0.0314</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6034±0.0000</t>
+          <t>0.6339±0.0099</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7403±0.0000</t>
+          <t>0.7234±0.0120</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.4234±0.0000</t>
+          <t>0.5553±0.0415</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7321±0.0000</t>
+          <t>0.7446±0.0242</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4743±0.0000</t>
+          <t>0.6504±0.0084</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.5723±0.0000</t>
+          <t>0.6662±0.0370</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6737±0.0000</t>
+          <t>0.6740±0.0263</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6883±0.0000</t>
+          <t>0.6566±0.0445</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.8138±0.0000</t>
+          <t>0.7834±0.0070</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.8326±0.0092</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.8326±0.0092</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.8326±0.0092</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8076±0.0000</t>
+          <t>0.7950±0.0191</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8552±0.0000</t>
+          <t>0.8360±0.0044</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7705±0.0000</t>
+          <t>0.8150±0.0107</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.4531±0.0000</t>
+          <t>0.5100±0.0386</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6759±0.0191</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6327±0.0000</t>
+          <t>0.6533±0.0203</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6538±0.0000</t>
+          <t>0.6595±0.0282</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6834±0.0137</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6798±0.0000</t>
+          <t>0.6886±0.0157</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.6678±0.0000</t>
+          <t>0.6920±0.0123</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7336±0.0000</t>
+          <t>0.7049±0.0232</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7336±0.0000</t>
+          <t>0.7049±0.0232</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7336±0.0000</t>
+          <t>0.7049±0.0232</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.6608±0.0000</t>
+          <t>0.6825±0.0104</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7796±0.0000</t>
+          <t>0.8293±0.0179</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7208±0.0000</t>
+          <t>0.6673±0.0124</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5622±0.0000</t>
+          <t>0.5138±0.0298</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7796±0.0000</t>
+          <t>0.8280±0.0318</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4886±0.0000</t>
+          <t>0.5727±0.0621</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5352±0.0000</t>
+          <t>0.6482±0.0513</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6305±0.0000</t>
+          <t>0.6836±0.0176</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6726±0.0000</t>
+          <t>0.7109±0.0206</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8202±0.0000</t>
+          <t>0.8303±0.0264</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8581±0.0000</t>
+          <t>0.8391±0.0097</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8581±0.0000</t>
+          <t>0.8391±0.0097</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8581±0.0000</t>
+          <t>0.8391±0.0097</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8349±0.0000</t>
+          <t>0.8391±0.0301</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8264±0.0000</t>
+          <t>0.8681±0.0081</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8479±0.0000</t>
+          <t>0.8398±0.0154</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6245±0.0000</t>
+          <t>0.5463±0.0215</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6848±0.0000</t>
+          <t>0.6940±0.0230</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.6508±0.0000</t>
+          <t>0.6617±0.0118</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6657±0.0000</t>
+          <t>0.6619±0.0172</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6762±0.0000</t>
+          <t>0.6813±0.0150</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.6894±0.0203</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6837±0.0000</t>
+          <t>0.6807±0.0219</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.6866±0.0150</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.6866±0.0150</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.6866±0.0150</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6750±0.0219</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8076±0.0000</t>
+          <t>0.8270±0.0041</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6740±0.0000</t>
+          <t>0.6690±0.0098</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.6051±0.0000</t>
+          <t>0.5977±0.0147</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6884±0.0000</t>
+          <t>0.7008±0.0211</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6390±0.0000</t>
+          <t>0.6535±0.0154</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6414±0.0000</t>
+          <t>0.6557±0.0228</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6766±0.0000</t>
+          <t>0.6819±0.0191</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6819±0.0189</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6931±0.0000</t>
+          <t>0.6884±0.0243</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6890±0.0000</t>
+          <t>0.6848±0.0267</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6890±0.0000</t>
+          <t>0.6848±0.0267</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6890±0.0000</t>
+          <t>0.6848±0.0267</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6864±0.0000</t>
+          <t>0.6788±0.0304</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7571±0.0087</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6863±0.0000</t>
+          <t>0.6772±0.0219</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5994±0.0000</t>
+          <t>0.5976±0.0178</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7528±0.0000</t>
+          <t>0.7561±0.0215</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4830±0.0000</t>
+          <t>0.5443±0.0666</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5696±0.0000</t>
+          <t>0.6658±0.0188</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6450±0.0000</t>
+          <t>0.7084±0.0415</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.6426±0.0000</t>
+          <t>0.6769±0.0172</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7659±0.0000</t>
+          <t>0.7848±0.0255</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.7503±0.0193</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.7503±0.0193</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.7503±0.0193</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7894±0.0000</t>
+          <t>0.7771±0.0175</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7740±0.0000</t>
+          <t>0.7817±0.0134</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7604±0.0000</t>
+          <t>0.7350±0.0152</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6406±0.0000</t>
+          <t>0.5974±0.0254</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7335±0.0000</t>
+          <t>0.7041±0.0444</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5461±0.0000</t>
+          <t>0.6868±0.0206</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7045±0.0000</t>
+          <t>0.6940±0.0146</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7214±0.0000</t>
+          <t>0.7168±0.0195</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7172±0.0000</t>
+          <t>0.7182±0.0200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7273±0.0000</t>
+          <t>0.7014±0.0381</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7021±0.0223</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7021±0.0223</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7021±0.0223</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7253±0.0000</t>
+          <t>0.7068±0.0456</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6299±0.0000</t>
+          <t>0.6596±0.0235</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7712±0.0000</t>
+          <t>0.7079±0.0074</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.5083±0.0000</t>
+          <t>0.6131±0.0187</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7689±0.0000</t>
+          <t>0.7500±0.0414</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.4870±0.0000</t>
+          <t>0.6722±0.0180</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5513±0.0000</t>
+          <t>0.6850±0.0684</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7128±0.0000</t>
+          <t>0.7045±0.0309</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7273±0.0000</t>
+          <t>0.6694±0.0748</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8059±0.0000</t>
+          <t>0.7772±0.0041</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7868±0.0000</t>
+          <t>0.8281±0.0116</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7868±0.0000</t>
+          <t>0.8281±0.0116</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7868±0.0000</t>
+          <t>0.8281±0.0116</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8092±0.0000</t>
+          <t>0.7864±0.0183</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8336±0.0000</t>
+          <t>0.8197±0.0047</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7657±0.0000</t>
+          <t>0.7979±0.0123</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5248±0.0000</t>
+          <t>0.5682±0.0465</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7259±0.0000</t>
+          <t>0.7166±0.0251</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6254±0.0000</t>
+          <t>0.7037±0.0264</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7153±0.0000</t>
+          <t>0.7063±0.0270</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7099±0.0000</t>
+          <t>0.7148±0.0136</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7186±0.0000</t>
+          <t>0.7199±0.0186</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.6925±0.0225</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7438±0.0000</t>
+          <t>0.7070±0.0158</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7438±0.0000</t>
+          <t>0.7070±0.0158</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7438±0.0000</t>
+          <t>0.7070±0.0158</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7152±0.0000</t>
+          <t>0.6965±0.0399</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7893±0.0000</t>
+          <t>0.8327±0.0242</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7280±0.0000</t>
+          <t>0.6698±0.0204</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5973±0.0000</t>
+          <t>0.5839±0.0223</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7828±0.0000</t>
+          <t>0.8171±0.0391</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4943±0.0000</t>
+          <t>0.5781±0.0603</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.6451±0.0497</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5904±0.0000</t>
+          <t>0.7161±0.0196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7114±0.0000</t>
+          <t>0.7297±0.0191</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8154±0.0000</t>
+          <t>0.8199±0.0328</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8488±0.0000</t>
+          <t>0.8278±0.0108</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8488±0.0000</t>
+          <t>0.8278±0.0108</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8488±0.0000</t>
+          <t>0.8278±0.0108</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8276±0.0000</t>
+          <t>0.8288±0.0347</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8307±0.0000</t>
+          <t>0.8625±0.0065</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8333±0.0000</t>
+          <t>0.8215±0.0095</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6692±0.0000</t>
+          <t>0.6262±0.0128</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7191±0.0263</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6851±0.0000</t>
+          <t>0.6970±0.0096</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.6925±0.0322</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7155±0.0000</t>
+          <t>0.7134±0.0170</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7162±0.0000</t>
+          <t>0.7219±0.0218</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7256±0.0000</t>
+          <t>0.7070±0.0401</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.6948±0.0397</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.6948±0.0397</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.6948±0.0397</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7257±0.0000</t>
+          <t>0.6991±0.0474</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8019±0.0000</t>
+          <t>0.8094±0.0098</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6921±0.0000</t>
+          <t>0.6848±0.0382</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6173±0.0000</t>
+          <t>0.6222±0.0288</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7167±0.0262</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6531±0.0000</t>
+          <t>0.6951±0.0249</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6986±0.0000</t>
+          <t>0.7020±0.0206</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7129±0.0000</t>
+          <t>0.7137±0.0215</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7146±0.0000</t>
+          <t>0.7126±0.0210</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7341±0.0000</t>
+          <t>0.7067±0.0448</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7306±0.0000</t>
+          <t>0.7033±0.0497</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7306±0.0000</t>
+          <t>0.7033±0.0497</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7306±0.0000</t>
+          <t>0.7033±0.0497</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7297±0.0000</t>
+          <t>0.6990±0.0534</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7458±0.0000</t>
+          <t>0.7835±0.0107</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7343±0.0000</t>
+          <t>0.6842±0.0502</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6509±0.0000</t>
+          <t>0.6315±0.0187</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7518±0.0376</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4914±0.0000</t>
+          <t>0.5406±0.0594</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5480±0.0000</t>
+          <t>0.6598±0.0361</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6955±0.0000</t>
+          <t>0.7234±0.0269</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.7040±0.0176</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7739±0.0000</t>
+          <t>0.7795±0.0283</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7059±0.0238</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7059±0.0238</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7059±0.0238</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7972±0.0000</t>
+          <t>0.7791±0.0219</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7776±0.0000</t>
+          <t>0.7730±0.0101</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7183±0.0000</t>
+          <t>0.6815±0.0220</t>
         </is>
       </c>
     </row>
